--- a/public/assets/templates/statistics/统计汇总-跨区明细.xlsx
+++ b/public/assets/templates/statistics/统计汇总-跨区明细.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17700"/>
+    <workbookView windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="跨区明细" sheetId="2" r:id="rId1"/>
@@ -1189,7 +1189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1210,9 +1210,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1739,26 +1736,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AE22"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.88461538461539" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="2" width="14.5740740740741" customWidth="1"/>
-    <col min="3" max="3" width="17.3055555555556" customWidth="1"/>
+    <col min="2" max="2" width="14.5769230769231" customWidth="1"/>
+    <col min="3" max="3" width="17.3076923076923" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="7" max="7" width="24.8425925925926" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="12" max="12" width="61.4444444444444" customWidth="1"/>
-    <col min="14" max="14" width="13.8888888888889" customWidth="1"/>
-    <col min="17" max="20" width="9.66666666666667"/>
-    <col min="21" max="21" width="18.4444444444444" customWidth="1"/>
-    <col min="22" max="22" width="22.4444444444444" customWidth="1"/>
-    <col min="23" max="23" width="17.4444444444444" customWidth="1"/>
-    <col min="24" max="24" width="19.6666666666667" customWidth="1"/>
+    <col min="7" max="7" width="24.8461538461538" customWidth="1"/>
+    <col min="8" max="8" width="23.5576923076923" customWidth="1"/>
+    <col min="9" max="9" width="11.2115384615385" customWidth="1"/>
+    <col min="10" max="10" width="20.8365384615385" customWidth="1"/>
+    <col min="11" max="11" width="20.9807692307692" customWidth="1"/>
+    <col min="12" max="12" width="45.8269230769231" customWidth="1"/>
+    <col min="13" max="13" width="13.6153846153846" customWidth="1"/>
+    <col min="14" max="14" width="13.8846153846154" customWidth="1"/>
+    <col min="15" max="15" width="11.8557692307692" customWidth="1"/>
+    <col min="16" max="16" width="12.6538461538462" customWidth="1"/>
+    <col min="17" max="17" width="12.1730769230769" customWidth="1"/>
+    <col min="18" max="18" width="12.0192307692308" customWidth="1"/>
+    <col min="19" max="19" width="11.8557692307692" customWidth="1"/>
+    <col min="20" max="20" width="14.4230769230769" customWidth="1"/>
+    <col min="21" max="21" width="18.4423076923077" customWidth="1"/>
+    <col min="22" max="22" width="22.4423076923077" customWidth="1"/>
+    <col min="23" max="23" width="17.4423076923077" customWidth="1"/>
+    <col min="24" max="24" width="19.6634615384615" customWidth="1"/>
+    <col min="25" max="25" width="24.1923076923077" customWidth="1"/>
     <col min="26" max="26" width="20" customWidth="1"/>
-    <col min="29" max="29" width="9.66666666666667"/>
-    <col min="31" max="31" width="9.66666666666667"/>
+    <col min="27" max="27" width="14.9038461538462" customWidth="1"/>
+    <col min="28" max="28" width="22.5961538461538" customWidth="1"/>
+    <col min="29" max="29" width="22.5865384615385" customWidth="1"/>
+    <col min="30" max="30" width="24.5192307692308" customWidth="1"/>
+    <col min="31" max="31" width="24.8365384615385" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="43.2" spans="1:31">
+    <row r="1" ht="38" customHeight="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1831,7 +1841,7 @@
       <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="4" t="s">
